--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF29D6D-5442-4D01-8A3D-D56FD46AB6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95F1033-AE29-4977-94BE-FD94F7E08983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
   <si>
     <t>TIM1</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -216,6 +216,10 @@
   </si>
   <si>
     <t>vsync</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>svsync</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1260,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA50990A-8917-4A1C-8E25-1E600BCC813B}">
-  <dimension ref="B2:P26"/>
+  <dimension ref="B2:P31"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
@@ -1287,11 +1291,11 @@
         <v>16</v>
       </c>
       <c r="C3" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2">
         <f>C3*2</f>
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.45">
@@ -1299,11 +1303,11 @@
         <v>15</v>
       </c>
       <c r="C4" s="2">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2">
         <f>C4*2</f>
-        <v>144</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
@@ -1455,6 +1459,9 @@
       <c r="D9" t="s">
         <v>25</v>
       </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
       <c r="G9" t="s">
         <v>26</v>
       </c>
@@ -1471,59 +1478,59 @@
       </c>
       <c r="C10" s="3">
         <f t="shared" ref="C10:P10" si="0">IF(C7="APB2",$D$4, $D$3)</f>
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3">
         <f t="shared" si="0"/>
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="K10" s="3">
         <f t="shared" si="0"/>
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="0"/>
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="0"/>
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="N10" s="3">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="O10" s="2">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="P10" s="2">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.45">
@@ -1537,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1564,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1578,13 +1585,13 @@
         <v>19</v>
       </c>
       <c r="C12">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>16665</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1599,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>39999</v>
+        <v>49999</v>
       </c>
       <c r="K12">
         <v>6867</v>
@@ -1630,27 +1637,27 @@
       </c>
       <c r="D13">
         <f t="shared" ref="D13:P13" si="1">D10/((D11+1)*(D12+1))</f>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>3.6001440057602306E-4</v>
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G13">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I13">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="J13">
         <f t="shared" si="1"/>
@@ -1658,15 +1665,15 @@
       </c>
       <c r="K13">
         <f t="shared" si="1"/>
-        <v>1.1648223645894001E-4</v>
+        <v>1.4560279557367502E-4</v>
       </c>
       <c r="L13">
         <f t="shared" si="1"/>
-        <v>1.1648223645894001E-4</v>
+        <v>1.4560279557367502E-4</v>
       </c>
       <c r="M13">
         <f t="shared" si="1"/>
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="N13">
         <f t="shared" si="1"/>
@@ -1674,11 +1681,11 @@
       </c>
       <c r="O13">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="P13">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.45">
@@ -1691,27 +1698,27 @@
       </c>
       <c r="D14">
         <f t="shared" ref="D14:P15" si="2">D13*1000</f>
-        <v>72000</v>
+        <v>90000</v>
       </c>
       <c r="E14">
         <f t="shared" si="2"/>
-        <v>72000</v>
+        <v>0.36001440057602307</v>
       </c>
       <c r="F14">
         <f t="shared" si="2"/>
-        <v>72000</v>
+        <v>90000</v>
       </c>
       <c r="G14">
         <f t="shared" si="2"/>
-        <v>72000</v>
+        <v>90000</v>
       </c>
       <c r="H14">
         <f t="shared" si="2"/>
-        <v>72000</v>
+        <v>90000</v>
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
-        <v>72000</v>
+        <v>90000</v>
       </c>
       <c r="J14">
         <f t="shared" si="2"/>
@@ -1719,15 +1726,15 @@
       </c>
       <c r="K14">
         <f t="shared" si="2"/>
-        <v>0.11648223645894001</v>
+        <v>0.14560279557367503</v>
       </c>
       <c r="L14">
         <f t="shared" si="2"/>
-        <v>0.11648223645894001</v>
+        <v>0.14560279557367503</v>
       </c>
       <c r="M14">
         <f t="shared" si="2"/>
-        <v>144000</v>
+        <v>180000</v>
       </c>
       <c r="N14">
         <f t="shared" si="2"/>
@@ -1735,11 +1742,11 @@
       </c>
       <c r="O14">
         <f t="shared" si="2"/>
-        <v>72000</v>
+        <v>90000</v>
       </c>
       <c r="P14">
         <f t="shared" si="2"/>
-        <v>72000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.45">
@@ -1752,27 +1759,27 @@
       </c>
       <c r="D15">
         <f t="shared" si="2"/>
-        <v>72000000</v>
+        <v>90000000</v>
       </c>
       <c r="E15">
         <f t="shared" si="2"/>
-        <v>72000000</v>
+        <v>360.01440057602309</v>
       </c>
       <c r="F15">
         <f t="shared" si="2"/>
-        <v>72000000</v>
+        <v>90000000</v>
       </c>
       <c r="G15">
         <f t="shared" si="2"/>
-        <v>72000000</v>
+        <v>90000000</v>
       </c>
       <c r="H15">
         <f t="shared" si="2"/>
-        <v>72000000</v>
+        <v>90000000</v>
       </c>
       <c r="I15">
         <f t="shared" si="2"/>
-        <v>72000000</v>
+        <v>90000000</v>
       </c>
       <c r="J15">
         <f t="shared" si="2"/>
@@ -1780,15 +1787,15 @@
       </c>
       <c r="K15">
         <f t="shared" si="2"/>
-        <v>116.48223645894001</v>
+        <v>145.60279557367502</v>
       </c>
       <c r="L15">
         <f t="shared" si="2"/>
-        <v>116.48223645894001</v>
+        <v>145.60279557367502</v>
       </c>
       <c r="M15">
         <f t="shared" si="2"/>
-        <v>144000000</v>
+        <v>180000000</v>
       </c>
       <c r="N15">
         <f t="shared" si="2"/>
@@ -1796,11 +1803,11 @@
       </c>
       <c r="O15">
         <f t="shared" si="2"/>
-        <v>72000000</v>
+        <v>90000000</v>
       </c>
       <c r="P15">
         <f t="shared" si="2"/>
-        <v>72000000</v>
+        <v>90000000</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.45">
@@ -1894,15 +1901,15 @@
       </c>
       <c r="C22" s="3">
         <f>IF(C19="APB2",$C$4, $C$3)</f>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D22" s="3">
         <f t="shared" ref="D22:E22" si="3">IF(D19="APB2",$C$4, $C$3)</f>
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E22" s="3">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>46</v>
@@ -1944,11 +1951,11 @@
       </c>
       <c r="C24">
         <f>C22/(C23)</f>
-        <v>18</v>
+        <v>22.5</v>
       </c>
       <c r="D24">
-        <f t="shared" ref="D24:E24" si="4">D22/(D23)</f>
-        <v>18</v>
+        <f t="shared" ref="D24" si="4">D22/(D23)</f>
+        <v>22.5</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>47</v>
@@ -1982,6 +1989,17 @@
       </c>
       <c r="D26" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="E30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="E31">
+        <f>1/E30*30</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95F1033-AE29-4977-94BE-FD94F7E08983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB85341C-85DD-4A2D-A0F3-C327E1FB1CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1264,18 +1264,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA50990A-8917-4A1C-8E25-1E600BCC813B}">
-  <dimension ref="B2:P31"/>
+  <dimension ref="B2:P26"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="10.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.08203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="9.9140625" customWidth="1"/>
+    <col min="3" max="16" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.45">
@@ -1544,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1562,10 +1556,10 @@
         <v>29</v>
       </c>
       <c r="K11">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -1591,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>16665</v>
+        <v>11717</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1609,10 +1603,10 @@
         <v>49999</v>
       </c>
       <c r="K12">
-        <v>6867</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>6867</v>
+        <v>0</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -1641,7 +1635,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="1"/>
-        <v>3.6001440057602306E-4</v>
+        <v>7.6804915514592934E-3</v>
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
@@ -1665,11 +1659,11 @@
       </c>
       <c r="K13">
         <f t="shared" si="1"/>
-        <v>1.4560279557367502E-4</v>
+        <v>180</v>
       </c>
       <c r="L13">
         <f t="shared" si="1"/>
-        <v>1.4560279557367502E-4</v>
+        <v>180</v>
       </c>
       <c r="M13">
         <f t="shared" si="1"/>
@@ -1702,7 +1696,7 @@
       </c>
       <c r="E14">
         <f t="shared" si="2"/>
-        <v>0.36001440057602307</v>
+        <v>7.6804915514592933</v>
       </c>
       <c r="F14">
         <f t="shared" si="2"/>
@@ -1726,11 +1720,11 @@
       </c>
       <c r="K14">
         <f t="shared" si="2"/>
-        <v>0.14560279557367503</v>
+        <v>180000</v>
       </c>
       <c r="L14">
         <f t="shared" si="2"/>
-        <v>0.14560279557367503</v>
+        <v>180000</v>
       </c>
       <c r="M14">
         <f t="shared" si="2"/>
@@ -1763,7 +1757,7 @@
       </c>
       <c r="E15">
         <f t="shared" si="2"/>
-        <v>360.01440057602309</v>
+        <v>7680.4915514592931</v>
       </c>
       <c r="F15">
         <f t="shared" si="2"/>
@@ -1787,11 +1781,11 @@
       </c>
       <c r="K15">
         <f t="shared" si="2"/>
-        <v>145.60279557367502</v>
+        <v>180000000</v>
       </c>
       <c r="L15">
         <f t="shared" si="2"/>
-        <v>145.60279557367502</v>
+        <v>180000000</v>
       </c>
       <c r="M15">
         <f t="shared" si="2"/>
@@ -1989,17 +1983,6 @@
       </c>
       <c r="D26" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="E30">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="E31">
-        <f>1/E30*30</f>
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB85341C-85DD-4A2D-A0F3-C327E1FB1CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CDF599-D927-4070-85F6-50E65D908CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CDF599-D927-4070-85F6-50E65D908CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3497A481-C257-471E-9F59-6ABA3934D24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mcu setting" sheetId="2" r:id="rId1"/>
@@ -909,7 +909,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>524812</xdr:colOff>
+      <xdr:colOff>521637</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>208188</xdr:rowOff>
     </xdr:to>

--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3497A481-C257-471E-9F59-6ABA3934D24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D4519B-E983-46A5-A822-05DE38A4B3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mcu setting" sheetId="2" r:id="rId1"/>
@@ -909,7 +909,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>521637</xdr:colOff>
+      <xdr:colOff>524812</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>208188</xdr:rowOff>
     </xdr:to>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>11717</v>
+        <v>719</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="1"/>
-        <v>7.6804915514592934E-3</v>
+        <v>0.125</v>
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="E14">
         <f t="shared" si="2"/>
-        <v>7.6804915514592933</v>
+        <v>125</v>
       </c>
       <c r="F14">
         <f t="shared" si="2"/>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E15">
         <f t="shared" si="2"/>
-        <v>7680.4915514592931</v>
+        <v>125000</v>
       </c>
       <c r="F15">
         <f t="shared" si="2"/>

--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/jig_mcu_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D4519B-E983-46A5-A822-05DE38A4B3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9176BF98-F734-4CCC-B2A8-3F2C964BDE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mcu setting" sheetId="2" r:id="rId1"/>
